--- a/output/pdf_financials_xlsx/PLAS.xlsx
+++ b/output/pdf_financials_xlsx/PLAS.xlsx
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.007043</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -864,7 +864,7 @@
         <v>-10.136364</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.065946</v>
+        <v>-3.072989</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.582858</v>
@@ -896,7 +896,7 @@
         <v>-10.063364</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.740662</v>
+        <v>-2.747705</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.257258</v>
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.53922</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.028162</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.07844</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.53922</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.028162</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.07844</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.048113</v>
+        <v>0.508893</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.028162</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.17844</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="49">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">

--- a/output/pdf_financials_xlsx/PLAS.xlsx
+++ b/output/pdf_financials_xlsx/PLAS.xlsx
@@ -4021,7 +4021,11 @@
           <t>Proceeds from share issuances 9</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -4618,7 +4622,11 @@
           <t>Proceeds from private placement 9</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
